--- a/hardware/jlcpcb/CPL_JLCPCB.xlsx
+++ b/hardware/jlcpcb/CPL_JLCPCB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,17 +986,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>40.500mm</t>
+          <t>72.500mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11.000mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1006,24 +1006,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>7.000mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>27.500mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1040,17 +1040,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.000mm</t>
+          <t>22.000mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>44.730mm</t>
+          <t>44.117mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1060,24 +1060,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>76.500mm</t>
+          <t>32.500mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>47.730mm</t>
+          <t>45.383mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1087,24 +1087,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>76.500mm</t>
+          <t>4.000mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8.730mm</t>
+          <t>11.000mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>77.000mm</t>
+          <t>4.000mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19.730mm</t>
+          <t>14.000mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1141,24 +1141,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7.000mm</t>
+          <t>14.000mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>27.500mm</t>
+          <t>24.000mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1168,24 +1168,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22.000mm</t>
+          <t>21.000mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>44.117mm</t>
+          <t>18.500mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1195,24 +1195,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>27.000mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.383mm</t>
+          <t>20.000mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1222,24 +1222,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4.000mm</t>
+          <t>21.500mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11.000mm</t>
+          <t>10.500mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1249,24 +1249,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4.000mm</t>
+          <t>26.000mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14.000mm</t>
+          <t>3.500mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14.000mm</t>
+          <t>8.000mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24.000mm</t>
+          <t>38.000mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1310,17 +1310,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21.000mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18.500mm</t>
+          <t>41.500mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>27.000mm</t>
+          <t>10.000mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20.000mm</t>
+          <t>41.500mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1357,24 +1357,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21.500mm</t>
+          <t>22.000mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10.500mm</t>
+          <t>50.500mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1384,24 +1384,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>26.000mm</t>
+          <t>28.000mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.500mm</t>
+          <t>50.500mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1411,24 +1411,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8.000mm</t>
+          <t>32.500mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>38.000mm</t>
+          <t>50.500mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1438,19 +1438,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>36.500mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,12 +1472,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10.000mm</t>
+          <t>44.000mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,17 +1499,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22.000mm</t>
+          <t>46.500mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>50.500mm</t>
+          <t>38.500mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1519,24 +1519,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>28.000mm</t>
+          <t>46.000mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>50.500mm</t>
+          <t>34.000mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>32.500mm</t>
+          <t>36.000mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>50.500mm</t>
+          <t>29.000mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>36.500mm</t>
+          <t>49.000mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>41.500mm</t>
+          <t>28.500mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1600,24 +1600,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>44.000mm</t>
+          <t>58.000mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>41.500mm</t>
+          <t>39.500mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1627,24 +1627,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>46.500mm</t>
+          <t>72.500mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>38.500mm</t>
+          <t>35.000mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1661,17 +1661,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>46.000mm</t>
+          <t>4.000mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>34.000mm</t>
+          <t>17.000mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1688,17 +1688,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>36.000mm</t>
+          <t>72.500mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>29.000mm</t>
+          <t>22.500mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1715,17 +1715,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>49.000mm</t>
+          <t>64.000mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>28.500mm</t>
+          <t>35.000mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1742,17 +1742,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>58.000mm</t>
+          <t>63.260mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>39.500mm</t>
+          <t>47.690mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1762,24 +1762,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>66.000mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>35.000mm</t>
+          <t>7.925mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4.000mm</t>
+          <t>68.190mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>17.000mm</t>
+          <t>22.240mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1823,17 +1823,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>72.500mm</t>
+          <t>33.000mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>22.500mm</t>
+          <t>5.500mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1850,17 +1850,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>64.000mm</t>
+          <t>43.000mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>35.000mm</t>
+          <t>24.000mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1869,195 +1869,6 @@
         </is>
       </c>
       <c r="E54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>63.260mm</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>47.690mm</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>U5</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>55.190mm</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>23.740mm</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>U6</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>66.000mm</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>7.925mm</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>47.190mm</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>13.740mm</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>U9</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>68.190mm</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>22.240mm</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>33.000mm</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>5.500mm</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>V2</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>43.000mm</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>24.000mm</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
